--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>687.</t>
+          <t>736.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2003.</t>
+          <t>2017.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>910.</t>
+          <t>959.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2380.</t>
+          <t>2394.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>736.</t>
+          <t>881.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2017.</t>
+          <t>1914.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>959.</t>
+          <t>1104.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2394.</t>
+          <t>2215.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>881.</t>
+          <t>1113.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1914.</t>
+          <t>1974.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1104.</t>
+          <t>1322.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -664,49 +664,49 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2215.</t>
+          <t>195.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>16-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15861542</v>
+        <v>31984321</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1113.</t>
+          <t>1424.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1974.</t>
+          <t>2124.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1322.</t>
+          <t>1616.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -664,47 +664,105 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2394.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>01-May-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Haryana Government||GJUS and T Hisar</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1,58,61,542</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>15861542</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>32</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>195.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>514.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>3,19,84,321</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>31984321</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1424.</t>
+          <t>288.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11-Jun-2026 12:30 PM</t>
+          <t>18-Jun-2026 10:45 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 05:00 PM</t>
+          <t>06-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02-Jul-2026 11:00 AM</t>
+          <t>07-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
+          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15,39,73,912</t>
+          <t>19,08,13,426</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>153973912</v>
+        <v>190813426</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -548,49 +548,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2124.</t>
+          <t>1578.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02-Jun-2026 11:00 AM</t>
+          <t>11-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17-Jun-2026 05:00 PM</t>
+          <t>01-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:00 PM</t>
+          <t>02-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
+          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9,61,59,224</t>
+          <t>15,39,73,912</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>96159224</v>
+        <v>153973912</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1616.</t>
+          <t>1898.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>02-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:00 PM</t>
+          <t>01-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:10 PM</t>
+          <t>02-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of school building in GSSS Dhareru] [20263F49E116 A6A8 4850 98F9 76FBCFD64BD91026SSP][2026_HBC_528054_1]</t>
+          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||HSSPP Panchkula</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,73,65,727</t>
+          <t>9,61,59,224</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17365727</v>
+        <v>96159224</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJD%2FD2%2FEIE7Rtc6PfuAfdHA%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2394.</t>
+          <t>2096.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>514.</t>
+          <t>926.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>288.</t>
+          <t>299.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1578.</t>
+          <t>1586.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1898.</t>
+          <t>1902.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2096.</t>
+          <t>2100.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>926.</t>
+          <t>937.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>299.</t>
+          <t>630.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1586.</t>
+          <t>1814.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1902.</t>
+          <t>2104.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2100.</t>
+          <t>2296.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>937.</t>
+          <t>1268.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>630.</t>
+          <t>635.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1814.</t>
+          <t>1795.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2104.</t>
+          <t>2085.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2296.</t>
+          <t>2277.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1268.</t>
+          <t>1273.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>635.</t>
+          <t>783.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1795.</t>
+          <t>1854.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2085.</t>
+          <t>2128.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2277.</t>
+          <t>2315.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1273.</t>
+          <t>1401.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>783.</t>
+          <t>1017.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1854.</t>
+          <t>1794.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2128.</t>
+          <t>1994.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2315.</t>
+          <t>45.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>15-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>16-Jul-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>9,55,97,065</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15861542</v>
+        <v>95597065</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -722,47 +722,105 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2160.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>01-May-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Haryana Government||GJUS and T Hisar</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1,58,61,542</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>15861542</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>32</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1401.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1516.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>3,19,84,321</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>31984321</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1017.</t>
+          <t>1138.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1794.</t>
+          <t>1795.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1994.</t>
+          <t>1989.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.</t>
+          <t>167.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2160.</t>
+          <t>2151.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1516.</t>
+          <t>1574.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Best Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -490,339 +490,49 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1138.</t>
+          <t>158.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-Jun-2026 10:45 AM</t>
+          <t>25-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06-Jul-2026 05:00 PM</t>
+          <t>02-Jul-2026 12:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>07-Jul-2026 03:00 PM</t>
+          <t>02-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
+          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19,08,13,426</t>
+          <t>1,98,80,991</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>190813426</v>
+        <v>19880991</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Best Tender</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>67</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1795.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>11-Jun-2026 12:30 PM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>01-Jul-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15,39,73,912</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>153973912</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Best Tender</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>62</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1989.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>02-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>01-Jul-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>9,61,59,224</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>96159224</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>167.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>22-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>15-Jul-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>16-Jul-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>9,55,97,065</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>95597065</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2151.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>01-May-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>26-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1,58,61,542</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>15861542</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>32</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1574.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>26-Jun-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3,19,84,321</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>31984321</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
         </is>
       </c>
     </row>

--- a/haryana_etenders.xlsx
+++ b/haryana_etenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,58 +481,754 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>117</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1697.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 10:45 AM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19,08,13,426</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>190813426</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1900.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9,61,59,224</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>96159224</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>75</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1097.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,98,80,991</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>19880991</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>65</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1802.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[Construction of EVM Warehouse Godown at Sector-2 Rohtak] [2026700D3E7D 53FE 43DE 9797 BE9913718D62653BAR][2026_HRY_528819_1]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Rohtak||EE PD-2 Rohtak</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10,51,01,701</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>105101701</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sry5YRZyJYErEnc0cX5iBww%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1540.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9,55,97,065</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>95597065</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>65</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2010.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>01-May-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Haryana Government||GJUS and T Hisar</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1,58,61,542</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>15861542</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>964.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[KITCHEN AND DIETARY SERVICES] [MCGMC/E-TENDER/2026/0003][2026_HRY_531897_1]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Maharishi Chyawan Medical College Koriawas Narnaul</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2,50,00,000</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SrJ9LRlgIfIaDXDKDCQLj5Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>35</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1300.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 05:50 PM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[Library Books] [MCGMC/E-TENDER/2026/0001][2026_HRY_531408_1]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Maharishi Chyawan Medical College Koriawas Narnaul</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2,50,00,000</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SyW7Kri2R3OCjLewhnCvr4w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>35</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1388.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Rough Cost Estimate for Various Construction works in Community Centre Sector-46 Ward No.20, Faridabad.] [202695CC0C9C FA7A 4968 BE73 7681F457F169284ULB][2026_HRY_531268_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Haryana Government||Urban Local Bodies||Faridabad</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1,93,54,683</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>19354683</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SloPzjrH0560YEBA7BHgYpA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1155.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[Service Contract] [PT/NRS/BH/14A][2026_HRY_531744_1]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Pt. Nekiram Sharma Govt. Medical College Bhiwani</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1,60,00,000</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si36wYGtipFe0hiuYvqSHPA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>32</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>34.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[Construction of residences for Judicial Officers in Judicial Court Complex at Sector 27, Pinjore in District- Panchkula] [2026AA86EF83 87EC 456A B50B E053BF193A04619BAR][2026_HRY_532891_1]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE NH Panchkula</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,93,28,386</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>49328386</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SUWmDcRlY6pUHY55gbdhOMA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Captured Backup</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Haryana eTenders</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>25</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>158.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 12:00 PM</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 02:00 PM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1,98,80,991</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>19880991</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1224.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[Construction of Community Centre on Bas-Bhangrola road in village Bhangrola in ward 06 under MC Manesar limit] [202614D22CA0 5C7D 4D88 AB43 52FC317DBA7B1809ULB][2026_HRY_531736_1]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Haryana Government||Urban Local Bodies||MC Manesar</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,68,83,803</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>76883803</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sq8qQOlcAQqZnmVMKtZjagw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>868.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[Const. of the building Mother and Child Block at Civil Hospital at Sonipat (Pdg. 01 No. 13 Passenger, 04 No. Bed Lift and 01 No. Dumbwaiter Lift). Recall] [202666510592 F004 436F ABE8 2656471BFB6E665BAR][2026_HRY_532088_1]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE (Elect.) Karnal||EE Elect. Karnal</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1,58,60,000</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>15860000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SXqMf39QjSypa7kfuDJeRgA%3D%3D</t>
         </is>
       </c>
     </row>
